--- a/ig/DM-AVRIL-2026/CodeSystem-TRE-R368-StatutRessource.xlsx
+++ b/ig/DM-AVRIL-2026/CodeSystem-TRE-R368-StatutRessource.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="104">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -217,7 +217,7 @@
     <t>Validé</t>
   </si>
   <si>
-    <t>Ressource approuvée officiellement par une personne ou un organisme. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
+    <t>Ressource approuvée officiellement par une personne ou un organisme. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS.  Ce statut s'adresse également à la ressource PresenceAbsence de l'usager.</t>
   </si>
   <si>
     <t>APPROUVE</t>
@@ -235,7 +235,7 @@
     <t>Planifié</t>
   </si>
   <si>
-    <t>Ressource organisée à l’avance pour une activité. Ce statut s'adresse à la ressource Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
+    <t>Ressource organisée à l’avance pour une activité. Ce statut s'adresse à la ressource Evenements liés à la prise en charge de l'individu dans une structure ESSMS. Ce statut s'adresse également à la ressource PresenceAbsence de l'usager.</t>
   </si>
   <si>
     <t>REALISE</t>
@@ -317,6 +317,15 @@
   </si>
   <si>
     <t>Etat de la ressource lors d’un arrêt temporaire. Ce statut s'adresse au projet personnalisé.</t>
+  </si>
+  <si>
+    <t>FACTURE</t>
+  </si>
+  <si>
+    <t>Facturé</t>
+  </si>
+  <si>
+    <t>Ressource pour laquelle une facture a été établie.</t>
   </si>
 </sst>
 </file>
@@ -732,7 +741,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -931,6 +940,20 @@
         <v>100</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
